--- a/output/iris_extract.xlsx
+++ b/output/iris_extract.xlsx
@@ -14,12 +14,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>index</t>
   </si>
   <si>
-    <t>species</t>
+    <t>planet</t>
   </si>
   <si>
     <t>description</t>
@@ -31,10 +31,22 @@
     <t>number of relatives</t>
   </si>
   <si>
-    <t>setosa</t>
-  </si>
-  <si>
-    <t>versicolor</t>
+    <t>Earth</t>
+  </si>
+  <si>
+    <t>Neptune</t>
+  </si>
+  <si>
+    <t>Venus</t>
+  </si>
+  <si>
+    <t>Jupiter</t>
+  </si>
+  <si>
+    <t>Uranus</t>
+  </si>
+  <si>
+    <t>Mars</t>
   </si>
   <si>
     <t>spinosa</t>
@@ -65,9 +77,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -121,21 +132,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -439,26 +444,26 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10.7109375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="40.7109375" style="3" customWidth="1"/>
-    <col min="4" max="4" width="5.7109375" style="4" customWidth="1"/>
-    <col min="5" max="5" width="19.7109375" style="5" customWidth="1"/>
+    <col min="2" max="2" width="7.7109375" customWidth="1"/>
+    <col min="3" max="3" width="40.7109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="5.7109375" customWidth="1"/>
+    <col min="5" max="5" width="19.7109375" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
     </row>
@@ -466,16 +471,16 @@
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="4">
+      <c r="C2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2">
         <v>1</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2" s="3">
         <v>1000</v>
       </c>
     </row>
@@ -483,16 +488,16 @@
       <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="4">
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3">
         <v>2.19</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="3">
         <v>500</v>
       </c>
     </row>
@@ -500,16 +505,16 @@
       <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="4">
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4">
         <v>3</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="3">
         <v>739</v>
       </c>
     </row>
@@ -517,16 +522,16 @@
       <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="4">
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5">
         <v>4.1</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="3">
         <v>13292</v>
       </c>
     </row>
@@ -534,16 +539,16 @@
       <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="4">
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6">
         <v>5</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="3">
         <v>58392</v>
       </c>
     </row>
@@ -551,16 +556,16 @@
       <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="4">
+      <c r="B7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7">
         <v>5.38</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="3">
         <v>531</v>
       </c>
     </row>
@@ -568,20 +573,30 @@
       <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8" s="4">
+      <c r="B8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8">
         <v>6</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="3">
         <v>33</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="A2:A1000">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFFF7128"/>
+        <color rgb="FFFFEF9C"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>